--- a/04_tiempos.xlsx
+++ b/04_tiempos.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiempos" sheetId="1" r:id="R9212b3a5a59a4c05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="2" r:id="R2aa42045660d4228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiempos" sheetId="1" r:id="Rbe9034a80e8548cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="2" r:id="R7ee2f0696203497c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -60,7 +60,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -115,6 +115,7 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1080,7 +1081,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G23" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H23" s="21" t="str">
         <x:v>Media</x:v>
@@ -1116,7 +1117,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G24" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H24" s="21" t="str">
         <x:v>Media</x:v>
@@ -1152,7 +1153,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G25" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H25" s="21" t="str">
         <x:v>Media</x:v>
@@ -1188,7 +1189,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G26" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H26" s="21" t="str">
         <x:v>Media</x:v>
@@ -1226,7 +1227,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G27" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H27" s="21" t="str">
         <x:v>Media</x:v>
@@ -1706,7 +1707,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G40" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H40" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1744,7 +1745,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G41" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H41" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1782,7 +1783,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G42" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H42" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1820,7 +1821,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G43" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H43" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1856,7 +1857,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G44" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H44" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1892,7 +1893,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G45" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H45" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1928,7 +1929,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G46" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H46" s="21" t="str">
         <x:v>Baja</x:v>
@@ -1966,7 +1967,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G47" s="21" t="str">
-        <x:v>Civil</x:v>
+        <x:v>Novia</x:v>
       </x:c>
       <x:c r="H47" s="21" t="str">
         <x:v>Baja</x:v>
@@ -3844,7 +3845,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G98" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H98" s="21" t="str">
         <x:v>Alta</x:v>
@@ -3880,7 +3881,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G99" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H99" s="21" t="str">
         <x:v>Alta</x:v>
@@ -3918,7 +3919,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G100" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H100" s="21" t="str">
         <x:v>Alta</x:v>
@@ -3956,7 +3957,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G101" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H101" s="21" t="str">
         <x:v>Alta</x:v>
@@ -3992,7 +3993,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G102" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H102" s="21" t="str">
         <x:v>Alta</x:v>
@@ -4030,7 +4031,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G103" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H103" s="21" t="str">
         <x:v>Alta</x:v>
@@ -4066,7 +4067,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G104" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H104" s="21" t="str">
         <x:v>Alta</x:v>
@@ -6248,7 +6249,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G163" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H163" s="21" t="str">
         <x:v>Media</x:v>
@@ -6284,7 +6285,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G164" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H164" s="21" t="str">
         <x:v>Media</x:v>
@@ -6320,7 +6321,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G165" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H165" s="21" t="str">
         <x:v>Media</x:v>
@@ -6356,7 +6357,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G166" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H166" s="21" t="str">
         <x:v>Media</x:v>
@@ -6392,7 +6393,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G167" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H167" s="21" t="str">
         <x:v>Media</x:v>
@@ -6428,7 +6429,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G168" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H168" s="21" t="str">
         <x:v>Media</x:v>
@@ -6466,7 +6467,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G169" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H169" s="21" t="str">
         <x:v>Media</x:v>
@@ -6504,7 +6505,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G170" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H170" s="21" t="str">
         <x:v>Media</x:v>
@@ -6540,7 +6541,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G171" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H171" s="21" t="str">
         <x:v>Media</x:v>
@@ -6578,7 +6579,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G172" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H172" s="21" t="str">
         <x:v>Media</x:v>
@@ -6616,7 +6617,7 @@
         <x:v>Corte</x:v>
       </x:c>
       <x:c r="G173" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H173" s="21" t="str">
         <x:v>Media</x:v>
@@ -6652,7 +6653,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G174" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H174" s="21" t="str">
         <x:v>Media</x:v>
@@ -6690,7 +6691,7 @@
         <x:v>Ensamblaje</x:v>
       </x:c>
       <x:c r="G175" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H175" s="21" t="str">
         <x:v>Media</x:v>
@@ -6728,7 +6729,7 @@
         <x:v>Acabados y detalles</x:v>
       </x:c>
       <x:c r="G176" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H176" s="21" t="str">
         <x:v>Media</x:v>
@@ -6764,7 +6765,7 @@
         <x:v>Planchado</x:v>
       </x:c>
       <x:c r="G177" s="21" t="str">
-        <x:v>Promoción</x:v>
+        <x:v>Gala</x:v>
       </x:c>
       <x:c r="H177" s="21" t="str">
         <x:v>Media</x:v>
@@ -9512,9 +9513,14 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="G5:G251">
+      <x:formula1>"Gala,Novia,Quinceañera"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51679bad803e42e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75285d6ff5f14a4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9575,6 +9581,14 @@
         <x:v>Los tiempos completados alimentan el criterio de desempeño histórico.</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="21" t="str">
+        <x:v>Tipo_Vestido</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="str">
+        <x:v>Clasificación limitada a Gala, Novia y Quinceañera.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
